--- a/billing_ledger.xlsx
+++ b/billing_ledger.xlsx
@@ -1,36 +1,177 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Irwen Dell G. Nulla\Downloads\BoardEase\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674FCBE7-175B-4759-9957-A985073F4C2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="0" yWindow="15" windowWidth="20730" windowHeight="11760" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Tenants" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Billing" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Rooms" sheetId="1" r:id="rId1"/>
+    <sheet name="Tenants" sheetId="2" r:id="rId2"/>
+    <sheet name="Billing" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="44">
+  <si>
+    <t>Room Number</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Base Rent</t>
+  </si>
+  <si>
+    <t>Max Occupancy</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>SingleRoom</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>SharedRoom</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Contact Number</t>
+  </si>
+  <si>
+    <t>Irwen Dell Nulla</t>
+  </si>
+  <si>
+    <t>09552566772</t>
+  </si>
+  <si>
+    <t>Camille Nulla</t>
+  </si>
+  <si>
+    <t>09685737685</t>
+  </si>
+  <si>
+    <t>James Reid</t>
+  </si>
+  <si>
+    <t>09123456789</t>
+  </si>
+  <si>
+    <t>Nadine Lustre</t>
+  </si>
+  <si>
+    <t>09091234512</t>
+  </si>
+  <si>
+    <t>Kathryn Bernardo</t>
+  </si>
+  <si>
+    <t>0981231879023</t>
+  </si>
+  <si>
+    <t>Roger Mancera</t>
+  </si>
+  <si>
+    <t>09092314321</t>
+  </si>
+  <si>
+    <t>Tenant</t>
+  </si>
+  <si>
+    <t>Room</t>
+  </si>
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>Rent Share</t>
+  </si>
+  <si>
+    <t>Utility Share</t>
+  </si>
+  <si>
+    <t>Total Amount</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Amount Paid</t>
+  </si>
+  <si>
+    <t>Date Paid</t>
+  </si>
+  <si>
+    <t>Balance</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>2026-10-10</t>
+  </si>
+  <si>
+    <t>2026-09-10</t>
+  </si>
+  <si>
+    <t>2026-09-15</t>
+  </si>
+  <si>
+    <t>PAID</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+  <si>
+    <t>2026-09-20</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>UNPAID</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,80 +190,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -410,51 +492,94 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="13.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Room Number</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Base Rent</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Max Occupancy</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SingleRoom</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>5000</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>5000</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>5000</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5">
+        <v>5000</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>5000</v>
+      </c>
+      <c r="D6">
         <v>1</v>
       </c>
     </row>
@@ -464,46 +589,88 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Contact Number</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Room Number</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Irwen Dell Nulla</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>09552566772</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -512,116 +679,185 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Tenant</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Room</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Rent Share</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Utility Share</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Total Amount</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Due Date</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Amount Paid</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Date Paid</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Balance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Irwen Dell Nulla</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E2" t="n">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>33</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2">
+        <v>5000</v>
+      </c>
+      <c r="E2">
         <v>1350</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>6350</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>5000</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J2" t="n">
+      <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2">
+        <v>5000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>38</v>
+      </c>
+      <c r="J2">
         <v>1350</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PAID</t>
-        </is>
+      <c r="K2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3">
+        <v>5000</v>
+      </c>
+      <c r="E3">
+        <v>1170</v>
+      </c>
+      <c r="F3">
+        <v>6170</v>
+      </c>
+      <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3">
+        <v>5000</v>
+      </c>
+      <c r="I3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J3">
+        <v>1170</v>
+      </c>
+      <c r="K3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4">
+        <v>5000</v>
+      </c>
+      <c r="E4">
+        <v>1440</v>
+      </c>
+      <c r="F4">
+        <v>6440</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4">
+        <v>6000</v>
+      </c>
+      <c r="I4" t="s">
+        <v>42</v>
+      </c>
+      <c r="J4">
+        <v>440</v>
+      </c>
+      <c r="K4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5">
+        <v>5000</v>
+      </c>
+      <c r="E5">
+        <v>1440</v>
+      </c>
+      <c r="F5">
+        <v>6440</v>
+      </c>
+      <c r="G5" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>6440</v>
+      </c>
+      <c r="K5" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>
